--- a/template_export.xlsx
+++ b/template_export.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huynx268/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/huynx268/Documents/Claude/Projects/Dev Full Stack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7513DEB-1B4E-6D43-83AF-58CA00F3633E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6060FD-3BA0-FF46-AF78-3B5461FC8691}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="29040" windowHeight="20580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="_56F9DC9755BA473782653E2940F9" sheetId="2" state="veryHidden" r:id="rId1"/>
-    <sheet name="CD - PL in cho ký nhận (" sheetId="8" r:id="rId2"/>
+    <sheet name="CD - PL in cho ký nhận" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_56F9DC9755BA473782653E2940F9FormId">"V6Pjw_ttoUmOduXsd8ZfwTMuH55bJJ5DuWEHs2W93ZZUNE1RQzRLSURHTVRORFlNVjEwS1I5TktLVi4u"</definedName>
@@ -687,6 +687,18 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -712,18 +724,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1085,87 +1085,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="3" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
     </row>
     <row r="2" spans="1:19" s="3" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="67"/>
-      <c r="M2" s="67"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
     </row>
     <row r="3" spans="1:19" s="3" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A3" s="65"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
+      <c r="A3" s="56"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="59"/>
+      <c r="K3" s="59"/>
+      <c r="L3" s="59"/>
+      <c r="M3" s="59"/>
     </row>
     <row r="4" spans="1:19" s="4" customFormat="1" ht="20.25" customHeight="1">
-      <c r="A4" s="58" t="s">
+      <c r="A4" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
+      <c r="B4" s="62"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
     </row>
     <row r="5" spans="1:19" s="5" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="59" t="s">
+      <c r="A5" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="63"/>
+      <c r="L5" s="63"/>
+      <c r="M5" s="63"/>
       <c r="N5" s="10"/>
       <c r="O5" s="10"/>
       <c r="P5" s="10"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="H8" s="52"/>
       <c r="I8" s="52" t="str">
-        <f t="shared" ref="I8:I14" si="0">IFERROR(F8+G8-H8,"")</f>
+        <f t="shared" ref="I8:I9" si="0">IFERROR(F8+G8-H8,"")</f>
         <v/>
       </c>
       <c r="J8" s="49" t="s">
@@ -1493,13 +1493,13 @@
       <c r="M14" s="14"/>
     </row>
     <row r="15" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A15" s="60" t="s">
+      <c r="A15" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="60"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="60"/>
-      <c r="E15" s="60"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
       <c r="F15" s="15">
         <f>SUM(F8:F14)</f>
         <v>9500000</v>
@@ -1522,22 +1522,22 @@
       <c r="M15" s="16"/>
     </row>
     <row r="16" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="65" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="62" t="s">
+      <c r="B16" s="65"/>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
-      <c r="I16" s="63"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="67"/>
+      <c r="J16" s="67"/>
+      <c r="K16" s="67"/>
+      <c r="L16" s="67"/>
       <c r="M16" s="17"/>
     </row>
     <row r="17" spans="1:22" ht="18.75" customHeight="1">
@@ -1546,31 +1546,31 @@
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="68"/>
+      <c r="H17" s="68"/>
+      <c r="I17" s="68"/>
     </row>
     <row r="18" spans="1:22" s="7" customFormat="1" ht="18.75" customHeight="1">
       <c r="A18" s="18"/>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57" t="s">
+      <c r="C18" s="60"/>
+      <c r="D18" s="60"/>
+      <c r="E18" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="56" t="s">
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="56"/>
-      <c r="L18" s="56"/>
-      <c r="M18" s="56"/>
+      <c r="K18" s="60"/>
+      <c r="L18" s="60"/>
+      <c r="M18" s="60"/>
       <c r="N18" s="19"/>
       <c r="O18" s="19"/>
     </row>
@@ -1860,12 +1860,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="F1:M1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:M2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:M3"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="E18:I18"/>
     <mergeCell ref="J18:M18"/>
@@ -1875,6 +1869,12 @@
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="F16:L16"/>
     <mergeCell ref="F17:I17"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="F1:M1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:M2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:M3"/>
   </mergeCells>
   <phoneticPr fontId="26" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
